--- a/src/main/resources/output.xlsx
+++ b/src/main/resources/output.xlsx
@@ -14,117 +14,300 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="37">
-  <si>
-    <t>9/11/2024</t>
-  </si>
-  <si>
-    <t>全聯</t>
-  </si>
-  <si>
-    <t>257</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="98">
+  <si>
+    <t>01/05/2025</t>
+  </si>
+  <si>
+    <t>家樂福買生活品</t>
+  </si>
+  <si>
+    <t>=1874-756</t>
   </si>
   <si>
     <t>生活開銷</t>
   </si>
   <si>
-    <t>酒精</t>
-  </si>
-  <si>
-    <t>109</t>
+    <t>01/02/2025</t>
+  </si>
+  <si>
+    <t>晚餐</t>
+  </si>
+  <si>
+    <t>351</t>
   </si>
   <si>
     <t>E</t>
   </si>
   <si>
-    <t>9/10/2024</t>
-  </si>
-  <si>
-    <t>九月房租</t>
-  </si>
-  <si>
-    <t>13300</t>
-  </si>
-  <si>
-    <t>電費(6/26~8/27)709度</t>
-  </si>
-  <si>
-    <t>1614</t>
-  </si>
-  <si>
-    <t>寶寶用品</t>
-  </si>
-  <si>
-    <t>1032</t>
-  </si>
-  <si>
-    <t>9/12/2024</t>
+    <t>01/01/2025</t>
+  </si>
+  <si>
+    <t>午餐全家</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>12/31/2024</t>
+  </si>
+  <si>
+    <t>嬰兒防踢被</t>
+  </si>
+  <si>
+    <t>835</t>
+  </si>
+  <si>
+    <t>飲料</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>全聯跨年火鍋料</t>
+  </si>
+  <si>
+    <t>989</t>
+  </si>
+  <si>
+    <t>12/29/2024</t>
+  </si>
+  <si>
+    <t>家樂福生活雜務</t>
+  </si>
+  <si>
+    <t>901</t>
+  </si>
+  <si>
+    <t>12/28/2024</t>
+  </si>
+  <si>
+    <t>汽車保養</t>
+  </si>
+  <si>
+    <t>4389</t>
+  </si>
+  <si>
+    <t>1900</t>
+  </si>
+  <si>
+    <t>12/27/2024</t>
+  </si>
+  <si>
+    <t>晚餐12min</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>12/26/2024</t>
+  </si>
+  <si>
+    <t>335</t>
+  </si>
+  <si>
+    <t>12/25/2024</t>
+  </si>
+  <si>
+    <t>午餐朱記</t>
+  </si>
+  <si>
+    <t>533</t>
+  </si>
+  <si>
+    <t>12/23/2024</t>
+  </si>
+  <si>
+    <t>行善汽車停車</t>
+  </si>
+  <si>
+    <t>10080(已經分期紀錄)</t>
+  </si>
+  <si>
+    <t>行善機車停車</t>
+  </si>
+  <si>
+    <t>900</t>
+  </si>
+  <si>
+    <t>464</t>
+  </si>
+  <si>
+    <t>01/03/2025</t>
   </si>
   <si>
     <t>早餐</t>
   </si>
   <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>飲料</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>冰</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>電子書</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>玩樂咖啡</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>全聯零食點心魔爪止汗膏</t>
-  </si>
-  <si>
-    <t>353</t>
-  </si>
-  <si>
-    <t>叮同加值</t>
+    <t>91</t>
+  </si>
+  <si>
+    <t>保費</t>
+  </si>
+  <si>
+    <t>26744</t>
+  </si>
+  <si>
+    <t>12/30/2024</t>
+  </si>
+  <si>
+    <t>溢乳墊</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>12/24/2024</t>
+  </si>
+  <si>
+    <t>衛生棉</t>
+  </si>
+  <si>
+    <t>393</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>廚房紙巾</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>12月薪水</t>
+  </si>
+  <si>
+    <t>86918</t>
+  </si>
+  <si>
+    <t>現金儲蓄</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>25-01_奉獻</t>
+  </si>
+  <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>01/04/2025</t>
+  </si>
+  <si>
+    <t>奶嘴</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>任天堂遊戲貓</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>買富爸爸窮爸爸書</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>InergieC4Duo充電</t>
+  </si>
+  <si>
+    <t>923</t>
+  </si>
+  <si>
+    <t>晚餐便當</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>約翰紅茶</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>好市多</t>
+  </si>
+  <si>
+    <t>1922</t>
+  </si>
+  <si>
+    <t>大樂透</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>711午餐</t>
+  </si>
+  <si>
+    <t>374</t>
+  </si>
+  <si>
+    <t>好市多跨年晚餐</t>
+  </si>
+  <si>
+    <t>950</t>
+  </si>
+  <si>
+    <t>高麗菜</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>果汁</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>午餐7-11</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>蛋糕</t>
   </si>
   <si>
     <t>160</t>
   </si>
   <si>
-    <t>泡澡桶</t>
-  </si>
-  <si>
-    <t>899</t>
-  </si>
-  <si>
-    <t>蝦皮整線圈插座轉頭</t>
-  </si>
-  <si>
-    <t>253</t>
-  </si>
-  <si>
-    <t>蝦皮小米無線充電器</t>
-  </si>
-  <si>
-    <t>1004</t>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Wemo</t>
+  </si>
+  <si>
+    <t>=33+39</t>
+  </si>
+  <si>
+    <t>午餐</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>剪頭髮</t>
+  </si>
+  <si>
+    <t>800</t>
+  </si>
+  <si>
+    <t>24-12_台哥大</t>
+  </si>
+  <si>
+    <t>998</t>
   </si>
 </sst>
 </file>
@@ -169,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -189,30 +372,30 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>3</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>3</v>
@@ -221,35 +404,191 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="E4" s="0"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>6</v>
-      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E6" s="0"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E7" s="0"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E8" s="0"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E9" s="0"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E12" s="0"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E13" s="0"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E14" s="0"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E15" s="0"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -258,18 +597,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="D1" t="s" s="0">
         <v>3</v>
@@ -278,13 +617,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>3</v>
@@ -293,13 +632,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>3</v>
@@ -308,48 +647,18 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>3</v>
       </c>
       <c r="E4" s="0"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="E5" s="0"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="E6" s="0"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -358,18 +667,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="D1" t="s" s="0">
         <v>3</v>
@@ -378,13 +687,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>3</v>
@@ -393,13 +702,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>3</v>
@@ -411,10 +720,10 @@
         <v>0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>3</v>
@@ -426,10 +735,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>3</v>
@@ -438,13 +747,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>3</v>
@@ -453,13 +762,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>3</v>
@@ -468,18 +777,273 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>3</v>
       </c>
       <c r="E8" s="0"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E9" s="0"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E10" s="0"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E11" s="0"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E12" s="0"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E13" s="0"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E14" s="0"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E15" s="0"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E16" s="0"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E17" s="0"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E18" s="0"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E19" s="0"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E20" s="0"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E21" s="0"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E22" s="0"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E23" s="0"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E24" s="0"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E25" s="0"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
